--- a/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/BROWN ADROGUE 1.xlsx
+++ b/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/BROWN ADROGUE 1.xlsx
@@ -329,798 +329,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1120140</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>899160</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="1 Imagen" descr="federico zaracho.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10469880" y="2994660"/>
-          <a:ext cx="1120140" cy="899160"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1158240</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="2 Imagen" descr="LEANDRO PRUÑONOSA.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10492740" y="3916680"/>
-          <a:ext cx="1135380" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1722120</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1219200</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>891540</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="3 Imagen" descr="LUCIANO DAWALDER.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="10462260" y="5737860"/>
-          <a:ext cx="1226820" cy="883920"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1173480</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>899160</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="4 Imagen" descr="FACUNDO MUÑOZ.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10469880" y="6637020"/>
-          <a:ext cx="1173480" cy="899160"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1722120</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1181100</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="5 Imagen" descr="URIEL VACAFLOR.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10462260" y="8481060"/>
-          <a:ext cx="1188720" cy="1013460"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1112520</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>1082040</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="6 Imagen" descr="LUCAS ESCOBAR.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10469880" y="11635740"/>
-          <a:ext cx="1112520" cy="1082040"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1135380</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="7 Imagen" descr="JESUS CRUZ.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10469880" y="12733020"/>
-          <a:ext cx="1135380" cy="1127760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1211580</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="8 Imagen" descr="ADRIAN SIMONI.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10469880" y="15674340"/>
-          <a:ext cx="1211580" cy="1112520"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1203959</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="9 Imagen" descr="NICOLAS RUIZ DIAZ.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10485120" y="16786860"/>
-          <a:ext cx="1188719" cy="937260"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>883920</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1196340</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="10 Imagen" descr="RODRIGO SANDOVAL.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10485120" y="17670780"/>
-          <a:ext cx="1181100" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>670560</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1181100</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="11 Imagen" descr="PROFE SERGIO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10469880" y="19278600"/>
-          <a:ext cx="1181100" cy="845820"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1219200</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="12 Imagen" descr="ELISEO SILVERO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10469880" y="4823460"/>
-          <a:ext cx="1219200" cy="922020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1158240</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="13 Imagen" descr="DAVID JARA.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10469880" y="7551420"/>
-          <a:ext cx="1158240" cy="922020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1143000</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="15 Imagen" descr="SANTINO CABRERA.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10469880" y="14752320"/>
-          <a:ext cx="1143000" cy="922020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1211580</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="16 Imagen" descr="PROFE GUSTAVO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10469880" y="20101560"/>
-          <a:ext cx="1211580" cy="723900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1714500</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1104900</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="17 Imagen" descr="NICOLAS TORIANO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10454640" y="13860780"/>
-          <a:ext cx="1120140" cy="967740"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1173480</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="18 Imagen" descr="BRIAN GONZALEZ.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10469880" y="10561320"/>
-          <a:ext cx="1173480" cy="1082040"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1082040" cy="935990"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="13 Imagen" descr="LUCA LOPEZ.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95F05035-292E-443D-A057-C84B2B6B68FB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10744200" y="16598900"/>
-          <a:ext cx="1082040" cy="935990"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
